--- a/Test.xlsx
+++ b/Test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="11655"/>
+    <workbookView windowWidth="20760" windowHeight="12060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -798,12 +798,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1456,7 +1453,7 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:12">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -1494,7 +1491,7 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:12">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -1532,7 +1529,7 @@
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:12">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" t="s">

--- a/Test.xlsx
+++ b/Test.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20760" windowHeight="12060"/>
+    <workbookView windowWidth="22305" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>file_id</t>
   </si>
@@ -65,6 +66,9 @@
     <t>remark</t>
   </si>
   <si>
+    <t>platform</t>
+  </si>
+  <si>
     <t>员工考勤表.xlsx</t>
   </si>
   <si>
@@ -183,6 +187,9 @@
   </si>
   <si>
     <t>客户合同（待上传）</t>
+  </si>
+  <si>
+    <t>AAA</t>
   </si>
 </sst>
 </file>
@@ -1330,15 +1337,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
     <col min="2" max="2" width="18.5" customWidth="1"/>
     <col min="3" max="3" width="39.375" customWidth="1"/>
+    <col min="5" max="5" width="79.375" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="10" max="11" width="31.5" customWidth="1"/>
+    <col min="12" max="12" width="29.875" customWidth="1"/>
+    <col min="13" max="13" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:12">
+    <row r="1" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1374,6 +1386,9 @@
       </c>
       <c r="L1" t="s">
         <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:12">
@@ -1381,37 +1396,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <v>1024000</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2">
         <v>1002</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:12">
@@ -1419,37 +1434,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>819200</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3">
         <v>1003</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:12">
@@ -1457,37 +1472,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4">
         <v>512000</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4">
         <v>1003</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:12">
@@ -1495,37 +1510,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>102400</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5">
         <v>1001</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:12">
@@ -1533,37 +1548,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6">
         <v>10485760</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6">
         <v>1003</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:12">
@@ -1571,72 +1586,72 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8">
         <v>1536000</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G8">
         <v>1001</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:12">
       <c r="B9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9">
         <v>1002</v>
       </c>
       <c r="H9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1646,4 +1661,64 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Test.xlsx
+++ b/Test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22305" windowHeight="12255"/>
+    <workbookView windowWidth="22335" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
   <si>
     <t>file_id</t>
   </si>
@@ -69,6 +69,12 @@
     <t>platform</t>
   </si>
   <si>
+    <t xml:space="preserve"> front</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>员工考勤表.xlsx</t>
   </si>
   <si>
@@ -187,6 +193,19 @@
   </si>
   <si>
     <t>客户合同（待上传）</t>
+  </si>
+  <si>
+    <t>总结</t>
+  </si>
+  <si>
+    <t>txt</t>
+  </si>
+  <si>
+    <t>2025-12-14 13:41:56.31715+09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">员工考勤表.xlsx,产品宣传图.jpg
+</t>
   </si>
   <si>
     <t>AAA</t>
@@ -805,12 +824,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1337,7 +1359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
@@ -1345,12 +1367,15 @@
     <col min="3" max="3" width="39.375" customWidth="1"/>
     <col min="5" max="5" width="79.375" customWidth="1"/>
     <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="8" max="8" width="17.125" customWidth="1"/>
+    <col min="9" max="9" width="12.625" customWidth="1"/>
     <col min="10" max="11" width="31.5" customWidth="1"/>
     <col min="12" max="12" width="29.875" customWidth="1"/>
-    <col min="13" max="13" width="9" style="1"/>
+    <col min="13" max="13" width="29.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:13">
+    <row r="1" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1389,6 +1414,12 @@
       </c>
       <c r="M1" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:12">
@@ -1396,37 +1427,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>1024000</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G2">
         <v>1002</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:12">
@@ -1434,37 +1465,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3">
         <v>819200</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <v>1003</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:12">
@@ -1472,37 +1503,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>512000</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4">
         <v>1003</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:12">
@@ -1510,37 +1541,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>102400</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5">
         <v>1001</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:12">
@@ -1548,37 +1579,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6">
         <v>10485760</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6">
         <v>1003</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:12">
@@ -1586,72 +1617,113 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8">
         <v>1536000</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>1001</v>
       </c>
       <c r="H8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:12">
       <c r="B9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <v>1002</v>
       </c>
       <c r="H9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:14">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
         <v>52</v>
+      </c>
+      <c r="D10">
+        <v>4251434</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10">
+        <v>1005</v>
+      </c>
+      <c r="H10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1674,7 +1746,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:1">

--- a/Test.xlsx
+++ b/Test.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
   <si>
     <t>file_id</t>
   </si>
@@ -195,16 +195,36 @@
     <t>客户合同（待上传）</t>
   </si>
   <si>
+    <t>总结.docx</t>
+  </si>
+  <si>
+    <t>/data/files/contract/总结.docx</t>
+  </si>
+  <si>
+    <t>txt</t>
+  </si>
+  <si>
+    <t>2025-12-14 13:41:56.31715+09</t>
+  </si>
+  <si>
     <t>总结</t>
   </si>
   <si>
-    <t>txt</t>
-  </si>
-  <si>
-    <t>2025-12-14 13:41:56.31715+09</t>
-  </si>
-  <si>
     <t xml:space="preserve">员工考勤表.xlsx,产品宣传图.jpg
+</t>
+  </si>
+  <si>
+    <t>拉电线.jpg</t>
+  </si>
+  <si>
+    <t>/data/files/contract/拉电线.jpg</t>
+  </si>
+  <si>
+    <t>2025-12-14 13:41:56.31715+10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logo.png
+产品宣传图.jpg
 </t>
   </si>
   <si>
@@ -824,7 +844,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -833,6 +853,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1359,7 +1382,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
@@ -1422,7 +1445,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:12">
+    <row r="2" customHeight="1" spans="1:15">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1460,7 +1483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:12">
+    <row r="3" customHeight="1" spans="1:15">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1498,7 +1521,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:12">
+    <row r="4" customHeight="1" spans="1:15">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1536,7 +1559,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:12">
+    <row r="5" customHeight="1" spans="1:15">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1574,7 +1597,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:12">
+    <row r="6" customHeight="1" spans="1:15">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1612,7 +1635,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:12">
+    <row r="8" customHeight="1" spans="1:15">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1650,7 +1673,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:12">
+    <row r="9" customHeight="1" spans="1:15">
       <c r="B9" t="s">
         <v>51</v>
       </c>
@@ -1685,7 +1708,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:14">
+    <row r="10" customHeight="1" spans="1:15">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1693,16 +1716,16 @@
         <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D10">
         <v>4251434</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>1005</v>
@@ -1714,16 +1737,57 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:15">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11">
+        <v>2222</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11">
+        <v>1002</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1746,7 +1810,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:1">

--- a/Test.xlsx
+++ b/Test.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="68">
   <si>
     <t>file_id</t>
   </si>
@@ -212,6 +212,9 @@
   <si>
     <t xml:space="preserve">员工考勤表.xlsx,产品宣传图.jpg
 </t>
+  </si>
+  <si>
+    <t>1,3</t>
   </si>
   <si>
     <t>拉电线.jpg</t>
@@ -226,6 +229,9 @@
     <t xml:space="preserve">logo.png
 产品宣传图.jpg
 </t>
+  </si>
+  <si>
+    <t>4,3</t>
   </si>
   <si>
     <t>AAA</t>
@@ -844,12 +850,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1396,6 +1405,7 @@
     <col min="12" max="12" width="29.875" customWidth="1"/>
     <col min="13" max="13" width="29.875" style="1" customWidth="1"/>
     <col min="14" max="14" width="13.25" customWidth="1"/>
+    <col min="15" max="15" width="121.5"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:15">
@@ -1672,6 +1682,9 @@
       <c r="L8" t="s">
         <v>50</v>
       </c>
+      <c r="O8" s="2">
+        <v>3.21315321312213e+50</v>
+      </c>
     </row>
     <row r="9" customHeight="1" spans="1:15">
       <c r="B9" t="s">
@@ -1745,8 +1758,11 @@
       <c r="L10" t="s">
         <v>59</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="3" t="s">
         <v>60</v>
+      </c>
+      <c r="O10" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:15">
@@ -1754,10 +1770,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11">
         <v>2222</v>
@@ -1778,16 +1794,19 @@
         <v>2</v>
       </c>
       <c r="J11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L11" t="s">
-        <v>61</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1810,7 +1829,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:1">

--- a/Test.xlsx
+++ b/Test.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="73">
   <si>
     <t>file_id</t>
   </si>
@@ -210,11 +210,11 @@
     <t>总结</t>
   </si>
   <si>
-    <t xml:space="preserve">员工考勤表.xlsx,产品宣传图.jpg
+    <t xml:space="preserve">员工考勤表.xlsx,产品宣传图.jpg,fhhtfhdgzz,gfdgsgdgfsffgdf,fsdfsdfdf
 </t>
   </si>
   <si>
-    <t>1,3</t>
+    <t>1gdesdfsdefsdfs,3gtdfgsfsdfgg,tfhydxgdgdfgdr,gsdfsfdsfstsef,hdfgdfrtstdgdgd</t>
   </si>
   <si>
     <t>拉电线.jpg</t>
@@ -232,6 +232,22 @@
   </si>
   <si>
     <t>4,3</t>
+  </si>
+  <si>
+    <t>XX哈哈.jpg</t>
+  </si>
+  <si>
+    <t>/data/files/contract/XX哈哈.jpg</t>
+  </si>
+  <si>
+    <t>2025-12-14 13:41:56.31715+11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">员工考勤表.xlsx,产品宣传图.jpg,fhhtfhdgzz,gfdgsgdgfsffgdf,fsdfsdfdf,gfhfhghfthhfgh,tfhdhdfh,产品宣传图.jpg
+</t>
+  </si>
+  <si>
+    <t>15321351311,1352145311353,313153130531,513513135103,313135151313,132514151435,45343442345,61463413643</t>
   </si>
   <si>
     <t>AAA</t>
@@ -850,7 +866,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -864,6 +880,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1391,7 +1413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
@@ -1404,8 +1426,8 @@
     <col min="10" max="11" width="31.5" customWidth="1"/>
     <col min="12" max="12" width="29.875" customWidth="1"/>
     <col min="13" max="13" width="29.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.25" customWidth="1"/>
-    <col min="15" max="15" width="121.5"/>
+    <col min="14" max="14" width="21.5" customWidth="1"/>
+    <col min="15" max="15" width="92.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:15">
@@ -1807,6 +1829,50 @@
       </c>
       <c r="O11" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:15">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12">
+        <v>2435135</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12">
+        <v>1550</v>
+      </c>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12" t="s">
+        <v>69</v>
+      </c>
+      <c r="L12" t="s">
+        <v>67</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1829,7 +1895,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:1">

--- a/Test.xlsx
+++ b/Test.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20760" windowHeight="12060"/>
+    <workbookView windowWidth="22335" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="73">
   <si>
     <t>file_id</t>
   </si>
@@ -65,6 +66,15 @@
     <t>remark</t>
   </si>
   <si>
+    <t>platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> front</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>员工考勤表.xlsx</t>
   </si>
   <si>
@@ -183,6 +193,64 @@
   </si>
   <si>
     <t>客户合同（待上传）</t>
+  </si>
+  <si>
+    <t>总结.docx</t>
+  </si>
+  <si>
+    <t>/data/files/contract/总结.docx</t>
+  </si>
+  <si>
+    <t>txt</t>
+  </si>
+  <si>
+    <t>2025-12-14 13:41:56.31715+09</t>
+  </si>
+  <si>
+    <t>总结</t>
+  </si>
+  <si>
+    <t xml:space="preserve">员工考勤表.xlsx,产品宣传图.jpg,fhhtfhdgzz,gfdgsgdgfsffgdf,fsdfsdfdf
+</t>
+  </si>
+  <si>
+    <t>1gdesdfsdefsdfs,3gtdfgsfsdfgg,tfhydxgdgdfgdr,gsdfsfdsfstsef,hdfgdfrtstdgdgd</t>
+  </si>
+  <si>
+    <t>拉电线.jpg</t>
+  </si>
+  <si>
+    <t>/data/files/contract/拉电线.jpg</t>
+  </si>
+  <si>
+    <t>2025-12-14 13:41:56.31715+10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logo.png
+产品宣传图.jpg
+</t>
+  </si>
+  <si>
+    <t>4,3</t>
+  </si>
+  <si>
+    <t>XX哈哈.jpg</t>
+  </si>
+  <si>
+    <t>/data/files/contract/XX哈哈.jpg</t>
+  </si>
+  <si>
+    <t>2025-12-14 13:41:56.31715+11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">员工考勤表.xlsx,产品宣传图.jpg,fhhtfhdgzz,gfdgsgdgfsffgdf,fsdfsdfdf,gfhfhghfthhfgh,tfhdhdfh,产品宣传图.jpg
+</t>
+  </si>
+  <si>
+    <t>15321351311,1352145311353,313153130531,513513135103,313135151313,132514151435,45343442345,61463413643</t>
+  </si>
+  <si>
+    <t>AAA</t>
   </si>
 </sst>
 </file>
@@ -798,12 +866,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1330,15 +1410,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
     <col min="2" max="2" width="18.5" customWidth="1"/>
     <col min="3" max="3" width="39.375" customWidth="1"/>
+    <col min="5" max="5" width="79.375" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="8" max="8" width="17.125" customWidth="1"/>
+    <col min="9" max="9" width="12.625" customWidth="1"/>
+    <col min="10" max="11" width="31.5" customWidth="1"/>
+    <col min="12" max="12" width="29.875" customWidth="1"/>
+    <col min="13" max="13" width="29.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5" customWidth="1"/>
+    <col min="15" max="15" width="92.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:12">
+    <row r="1" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1375,268 +1464,412 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:12">
+    <row r="2" customHeight="1" spans="1:15">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>1024000</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G2">
         <v>1002</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:12">
+    <row r="3" customHeight="1" spans="1:15">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3">
         <v>819200</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <v>1003</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:12">
+    <row r="4" customHeight="1" spans="1:15">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>512000</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G4">
         <v>1003</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:12">
+    <row r="5" customHeight="1" spans="1:15">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>102400</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G5">
         <v>1001</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:12">
+    <row r="6" customHeight="1" spans="1:15">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6">
         <v>10485760</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G6">
         <v>1003</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:12">
+    <row r="8" customHeight="1" spans="1:15">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D8">
         <v>1536000</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>1001</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="O8" s="2">
+        <v>3.21315321312213e+50</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:12">
+    <row r="9" customHeight="1" spans="1:15">
       <c r="B9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <v>1002</v>
       </c>
       <c r="H9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L9" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:15">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10">
+        <v>4251434</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10">
+        <v>1005</v>
+      </c>
+      <c r="H10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="O10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:15">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11">
+        <v>2222</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11">
+        <v>1002</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K11" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:15">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12">
+        <v>2435135</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12">
+        <v>1550</v>
+      </c>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12" t="s">
+        <v>69</v>
+      </c>
+      <c r="L12" t="s">
+        <v>67</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1646,4 +1879,64 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Test.xlsx
+++ b/Test.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Code\SqlTool\SqlTool\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F92387E-FC4B-4990-ABCE-AAD6C2403AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22335" windowHeight="12255"/>
+    <workbookView xWindow="3072" yWindow="12" windowWidth="18936" windowHeight="12948" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -256,14 +262,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,345 +272,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -618,255 +294,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -885,90 +319,162 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color theme="1"/>
       </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -979,7 +485,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1007,154 +513,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1404,30 +796,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.375" style="1"/>
-    <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="3" width="39.375" customWidth="1"/>
-    <col min="5" max="5" width="79.375" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="8" max="8" width="17.125" customWidth="1"/>
-    <col min="9" max="9" width="12.625" customWidth="1"/>
-    <col min="10" max="11" width="31.5" customWidth="1"/>
-    <col min="12" max="12" width="29.875" customWidth="1"/>
-    <col min="13" max="13" width="29.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5" customWidth="1"/>
-    <col min="15" max="15" width="92.75" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="39.33203125" customWidth="1"/>
+    <col min="5" max="5" width="79.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="11" width="31.44140625" customWidth="1"/>
+    <col min="12" max="12" width="29.88671875" customWidth="1"/>
+    <col min="13" max="13" width="29.88671875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.44140625" customWidth="1"/>
+    <col min="15" max="15" width="92.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:15">
+    <row r="1" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1474,7 +866,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:15">
+    <row r="2" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1512,7 +904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:15">
+    <row r="3" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1550,7 +942,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:15">
+    <row r="4" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1588,7 +980,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:15">
+    <row r="5" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1626,7 +1018,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:15">
+    <row r="6" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1664,8 +1056,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:15">
-      <c r="A8" s="1">
+    <row r="8" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>6</v>
       </c>
       <c r="B8" t="s">
@@ -1702,10 +1094,11 @@
         <v>50</v>
       </c>
       <c r="O8" s="2">
-        <v>3.21315321312213e+50</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:15">
+        <v>3.21315321312213E+50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
       <c r="B9" t="s">
         <v>51</v>
       </c>
@@ -1740,7 +1133,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:15">
+    <row r="10" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1784,7 +1177,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:15">
+    <row r="11" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1828,7 +1221,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:15">
+    <row r="12" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1876,67 +1269,66 @@
   <mergeCells count="1">
     <mergeCell ref="A8:A9"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Test.xlsx
+++ b/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Code\SqlTool\SqlTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F92387E-FC4B-4990-ABCE-AAD6C2403AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6D0BE0-129C-47B2-803B-C6EBD1D83433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3072" yWindow="12" windowWidth="18936" windowHeight="12948" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,24 +17,11 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="75">
   <si>
     <t>file_id</t>
   </si>
@@ -81,9 +68,6 @@
     <t>A</t>
   </si>
   <si>
-    <t>员工考勤表.xlsx</t>
-  </si>
-  <si>
     <t>/data/files/hr/2025/attendance.xlsx</t>
   </si>
   <si>
@@ -151,9 +135,6 @@
   </si>
   <si>
     <t>公司LOGO</t>
-  </si>
-  <si>
-    <t>产品介绍视频.mp4</t>
   </si>
   <si>
     <t>/data/files/video/product.mp4</t>
@@ -249,21 +230,38 @@
     <t>2025-12-14 13:41:56.31715+11</t>
   </si>
   <si>
+    <t>15321351311,1352145311353,313153130531,513513135103,313135151313,132514151435,45343442345,61463413643</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>产品介绍视频.mp4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>员工考勤表.xlsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品介绍视频.mp4,员工考勤表.xlsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">员工考勤表.xlsx,产品宣传图.jpg,fhhtfhdgzz,gfdgsgdgfsffgdf,fsdfsdfdf,gfhfhghfthhfgh,tfhdhdfh,产品宣传图.jpg
 </t>
-  </si>
-  <si>
-    <t>15321351311,1352145311353,313153130531,513513135103,313135151313,132514151435,45343442345,61463413643</t>
-  </si>
-  <si>
-    <t>AAA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +272,14 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -300,7 +306,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -317,6 +323,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -802,7 +814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="1"/>
@@ -819,7 +831,7 @@
     <col min="15" max="15" width="92.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -865,404 +877,410 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P1" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
       </c>
       <c r="D2">
         <v>1024000</v>
       </c>
       <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
         <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
       </c>
       <c r="G2">
         <v>1002</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
         <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
       </c>
       <c r="D3">
         <v>819200</v>
       </c>
       <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
         <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
       </c>
       <c r="G3">
         <v>1003</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
         <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
       </c>
       <c r="D4">
         <v>512000</v>
       </c>
       <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
         <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
       </c>
       <c r="G4">
         <v>1003</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
       </c>
       <c r="D5">
         <v>102400</v>
       </c>
       <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
         <v>36</v>
-      </c>
-      <c r="F5" t="s">
-        <v>37</v>
       </c>
       <c r="G5">
         <v>1001</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>39</v>
+      <c r="B6" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6">
         <v>10485760</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6">
         <v>1003</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
       </c>
       <c r="D8">
         <v>1536000</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G8">
         <v>1001</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O8" s="2">
         <v>3.21315321312213E+50</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
+    <row r="9" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
         <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
       </c>
       <c r="G9">
         <v>1002</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D10">
         <v>4251434</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>1005</v>
       </c>
       <c r="H10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I10">
         <v>1</v>
       </c>
       <c r="J10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="K10" t="s">
-        <v>58</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="O10" t="s">
         <v>59</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="O10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D11">
         <v>2222</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11">
         <v>1002</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
       <c r="J11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O11" t="s">
         <v>64</v>
       </c>
-      <c r="K11" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" t="s">
-        <v>62</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="O11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D12">
         <v>2435135</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G12">
         <v>1550</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L12" t="s">
-        <v>67</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1276,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1284,7 +1302,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1325,6 +1343,16 @@
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Test.xlsx
+++ b/Test.xlsx
@@ -1,22 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Code\SqlTool\SqlTool\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6D0BE0-129C-47B2-803B-C6EBD1D83433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3072" yWindow="12" windowWidth="18936" windowHeight="12948" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -68,6 +75,12 @@
     <t>A</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>员工考勤表.xlsx</t>
+  </si>
+  <si>
     <t>/data/files/hr/2025/attendance.xlsx</t>
   </si>
   <si>
@@ -137,6 +150,9 @@
     <t>公司LOGO</t>
   </si>
   <si>
+    <t>产品介绍视频.mp4</t>
+  </si>
+  <si>
     <t>/data/files/video/product.mp4</t>
   </si>
   <si>
@@ -180,6 +196,9 @@
   </si>
   <si>
     <t>客户合同（待上传）</t>
+  </si>
+  <si>
+    <t>产品介绍视频.mp4,员工考勤表.xlsx</t>
   </si>
   <si>
     <t>总结.docx</t>
@@ -230,38 +249,27 @@
     <t>2025-12-14 13:41:56.31715+11</t>
   </si>
   <si>
-    <t>15321351311,1352145311353,313153130531,513513135103,313135151313,132514151435,45343442345,61463413643</t>
-  </si>
-  <si>
-    <t>AAA</t>
-  </si>
-  <si>
-    <t>产品介绍视频.mp4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>员工考勤表.xlsx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品介绍视频.mp4,员工考勤表.xlsx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">员工考勤表.xlsx,产品宣传图.jpg,fhhtfhdgzz,gfdgsgdgfsffgdf,fsdfsdfdf,gfhfhghfthhfgh,tfhdhdfh,产品宣传图.jpg
 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15321351311,1352145311353,313153130531,513513135103,313135151313,132514151435,45343442345,61463413643</t>
+  </si>
+  <si>
+    <t>AAA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,29 +278,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -300,21 +631,269 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -325,168 +904,90 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -497,7 +998,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -525,40 +1026,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -572,7 +1187,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CEEACA"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -808,30 +1423,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="25.05" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" customWidth="1"/>
-    <col min="5" max="5" width="79.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
-    <col min="10" max="11" width="31.44140625" customWidth="1"/>
-    <col min="12" max="12" width="29.88671875" customWidth="1"/>
-    <col min="13" max="13" width="29.88671875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="21.44140625" customWidth="1"/>
-    <col min="15" max="15" width="92.77734375" customWidth="1"/>
+    <col min="1" max="1" width="10.3333333333333" style="1"/>
+    <col min="2" max="2" width="18.4416666666667" customWidth="1"/>
+    <col min="3" max="3" width="39.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="79.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="12.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="17.1083333333333" customWidth="1"/>
+    <col min="9" max="9" width="12.6666666666667" customWidth="1"/>
+    <col min="10" max="11" width="31.4416666666667" customWidth="1"/>
+    <col min="12" max="12" width="29.8833333333333" customWidth="1"/>
+    <col min="13" max="13" width="29.8833333333333" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.4416666666667" customWidth="1"/>
+    <col min="15" max="15" width="92.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" customHeight="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -877,486 +1492,491 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:16">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>71</v>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>1024000</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2">
         <v>1002</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:16">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>819200</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G3">
         <v>1003</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:16">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>512000</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4">
         <v>1003</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:16">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5">
         <v>102400</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G5">
         <v>1001</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:16">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>70</v>
+      <c r="B6" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D6">
         <v>10485760</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G6">
         <v>1003</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:16">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D8">
         <v>1536000</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G8">
         <v>1001</v>
       </c>
       <c r="H8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="2">
-        <v>3.21315321312213E+50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
+        <v>51</v>
+      </c>
+      <c r="O8" s="3">
+        <v>3.21315321312213e+50</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:16">
       <c r="B9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G9">
         <v>1002</v>
       </c>
       <c r="H9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L9" t="s">
-        <v>52</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:16">
       <c r="A10" s="1">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D10">
         <v>4251434</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>1005</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I10">
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L10" t="s">
-        <v>57</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="O10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:16">
       <c r="A11" s="1">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D11">
         <v>2222</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G11">
         <v>1002</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
       <c r="J11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L11" t="s">
-        <v>60</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="O11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:16">
       <c r="A12" s="1">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D12">
         <v>2435135</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G12">
         <v>1550</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L12" t="s">
-        <v>65</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A8:A9"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+      <formula1>$F$2:$F$12</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="1">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Test.xlsx
+++ b/Test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="15870" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="81">
   <si>
     <t>file_id</t>
   </si>
@@ -78,6 +78,12 @@
     <t>B</t>
   </si>
   <si>
+    <t>srcs（1:文件，2：目录）</t>
+  </si>
+  <si>
+    <t>rc</t>
+  </si>
+  <si>
     <t>员工考勤表.xlsx</t>
   </si>
   <si>
@@ -99,6 +105,9 @@
     <t>2025年12月员工考勤表</t>
   </si>
   <si>
+    <t>[{"field":"files","type":"files","value":"[{\"type\":1,\"value\":\"询问笔录,起诉意见书\"}]","value_data":{"files":[],"file":["询问笔录","起诉意见书"],"wsml":""}}]</t>
+  </si>
+  <si>
     <t>产品需求文档.docx</t>
   </si>
   <si>
@@ -117,6 +126,10 @@
     <t>V2.0产品需求文档</t>
   </si>
   <si>
+    <t xml:space="preserve">[{"field":"files","type":"files","value":"[{\"type\":1,\"value\":\"aaa\"},{\"type\":2,\"value\":\"aaa,vvb\"}]","value_data":{"files":[],"file":["aaa"],"wsml":["aaa","vvb"]}},{"field":"text_input","type":"qzscx","value":"","value_data":{"files":[],"file":"","wsml":""}}]
+</t>
+  </si>
+  <si>
     <t>产品宣传图.jpg</t>
   </si>
   <si>
@@ -135,6 +148,10 @@
     <t>首页产品宣传横幅</t>
   </si>
   <si>
+    <t xml:space="preserve">[{"field":"files","type":"files","value":"[{\"type\":1,\"value\":\"灼云间,无道书\"}]","value_data":{"files":[],"file":["灼云间","无道书"],"wsml":""}}]
+</t>
+  </si>
+  <si>
     <t>logo.png</t>
   </si>
   <si>
@@ -148,6 +165,10 @@
   </si>
   <si>
     <t>公司LOGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[{"field":"text_input","type":"qzscx","value":"52965a0a5a5cb211ddadd2a8d59c3d72,7408043CE588B211B8A3E2583A404532"}]
+</t>
   </si>
   <si>
     <t>产品介绍视频.mp4</t>
@@ -269,14 +290,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -749,160 +763,154 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1429,472 +1437,494 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25.05" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.3333333333333" style="1"/>
-    <col min="2" max="2" width="18.4416666666667" customWidth="1"/>
-    <col min="3" max="3" width="39.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="79.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="12.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="17.1083333333333" customWidth="1"/>
-    <col min="9" max="9" width="12.6666666666667" customWidth="1"/>
-    <col min="10" max="11" width="31.4416666666667" customWidth="1"/>
-    <col min="12" max="12" width="29.8833333333333" customWidth="1"/>
-    <col min="13" max="13" width="29.8833333333333" style="1" customWidth="1"/>
-    <col min="14" max="14" width="21.4416666666667" customWidth="1"/>
-    <col min="15" max="15" width="92.775" customWidth="1"/>
+    <col min="1" max="1" width="10.3333333333333" style="2"/>
+    <col min="2" max="2" width="18.4416666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="39.3333333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.375" style="2"/>
+    <col min="5" max="5" width="79.3333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.6666666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="17.1083333333333" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.6666666666667" style="2" customWidth="1"/>
+    <col min="10" max="11" width="31.4416666666667" style="2" customWidth="1"/>
+    <col min="12" max="13" width="29.8833333333333" style="2" customWidth="1"/>
+    <col min="14" max="14" width="21.4416666666667" style="2" customWidth="1"/>
+    <col min="15" max="15" width="92.775" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9" style="2"/>
+    <col min="17" max="17" width="160.375" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:16">
-      <c r="A1" s="1" t="s">
+    <row r="1" customHeight="1" spans="1:18">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:16">
-      <c r="A2" s="1">
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:18">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2">
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="2">
         <v>1024000</v>
       </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2">
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2">
         <v>1002</v>
       </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2">
+      <c r="H2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="2">
         <v>1</v>
       </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:16">
-      <c r="A3" s="1">
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:18">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="2">
+        <v>819200</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1003</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3">
-        <v>819200</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3">
+      <c r="K3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:18">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="2">
+        <v>512000</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2">
         <v>1003</v>
       </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3">
+      <c r="H4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="2">
         <v>1</v>
       </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="J4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:18">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="2">
+        <v>102400</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1001</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:18">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10485760</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1003</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:18">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1536000</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1001</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="2">
+        <v>2</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="4">
+        <v>3.21315321312213e+50</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:18">
+      <c r="B9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:16">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="F9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4">
-        <v>512000</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4">
-        <v>1003</v>
-      </c>
-      <c r="H4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4">
+      <c r="G9" s="2">
+        <v>1002</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:18">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4251434</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1005</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="2">
         <v>1</v>
       </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:16">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="J10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:18">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2222</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D5">
-        <v>102400</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1002</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5">
-        <v>1001</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:16">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6">
-        <v>10485760</v>
-      </c>
-      <c r="E6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6">
-        <v>1003</v>
-      </c>
-      <c r="H6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:16">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8">
-        <v>1536000</v>
-      </c>
-      <c r="E8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8">
-        <v>1001</v>
-      </c>
-      <c r="H8" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8">
+      <c r="I11" s="2">
         <v>2</v>
       </c>
-      <c r="J8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" t="s">
-        <v>51</v>
-      </c>
-      <c r="O8" s="3">
-        <v>3.21315321312213e+50</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:16">
-      <c r="B9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9">
+      <c r="J11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:18">
+      <c r="A12" s="2">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2435135</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1550</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="2">
         <v>0</v>
       </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9">
-        <v>1002</v>
-      </c>
-      <c r="H9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" t="s">
-        <v>55</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:16">
-      <c r="A10" s="1">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10">
-        <v>4251434</v>
-      </c>
-      <c r="E10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10">
-        <v>1005</v>
-      </c>
-      <c r="H10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>60</v>
-      </c>
-      <c r="K10" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" t="s">
-        <v>61</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="O10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:16">
-      <c r="A11" s="1">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11">
-        <v>2222</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11">
-        <v>1002</v>
-      </c>
-      <c r="H11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11">
-        <v>2</v>
-      </c>
-      <c r="J11" t="s">
-        <v>66</v>
-      </c>
-      <c r="K11" t="s">
-        <v>66</v>
-      </c>
-      <c r="L11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="O11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:16">
-      <c r="A12" s="1">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12">
-        <v>2435135</v>
-      </c>
-      <c r="E12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12">
-        <v>1550</v>
-      </c>
-      <c r="H12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>71</v>
-      </c>
-      <c r="K12" t="s">
-        <v>71</v>
-      </c>
-      <c r="L12" t="s">
-        <v>69</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>73</v>
+      <c r="J12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1922,7 +1952,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:1">

--- a/Test.xlsx
+++ b/Test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15870" windowHeight="12975"/>
+    <workbookView windowWidth="21690" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Test.xlsx
+++ b/Test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21690" windowHeight="12975"/>
+    <workbookView windowWidth="20160" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="83">
   <si>
     <t>file_id</t>
   </si>
@@ -105,7 +105,7 @@
     <t>2025年12月员工考勤表</t>
   </si>
   <si>
-    <t>[{"field":"files","type":"files","value":"[{\"type\":1,\"value\":\"询问笔录,起诉意见书\"}]","value_data":{"files":[],"file":["询问笔录","起诉意见书"],"wsml":""}}]</t>
+    <t>[{"field":"files","type":"files","value":"[{\"type\":1,\"value\":\"撰文,小隶"}]","value_data":{"files":[],"file":["撰文","小隶"],"wsml":""}}]</t>
   </si>
   <si>
     <t>产品需求文档.docx</t>
@@ -187,6 +187,12 @@
   </si>
   <si>
     <t>V2.0产品介绍视频</t>
+  </si>
+  <si>
+    <t>[{"field":"files","type":"files","value_data":{"files":[],"file":[""],"wsml":""},"value":"[{\"type\":1,\"value\":\"\"}]"},{"field":"content","type":"qzscx","value_data":{"files":[],"file":"","wsml":""},"value":"1,2,3"}]</t>
+  </si>
+  <si>
+    <t>[{"field":"files","type":"files","value_data":{"files":[],"file":["","觉文"],"wsml":""},"value":"[{\"type\":1,\"value\":\",觉文\"}]"},{"field":"content","type":"qzscx","value":"5,3,7,2,1,9"}]</t>
   </si>
   <si>
     <t>旧版财务报告.pdf</t>
@@ -1715,31 +1721,39 @@
       <c r="L6" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="Q6" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:18">
+      <c r="Q7" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="8" customHeight="1" spans="1:18">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2">
         <v>1536000</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8" s="2">
         <v>1001</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I8" s="2">
         <v>2</v>
@@ -1751,7 +1765,7 @@
         <v>23</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O8" s="4">
         <v>3.21315321312213e+50</v>
@@ -1759,10 +1773,10 @@
     </row>
     <row r="9" customHeight="1" spans="1:18">
       <c r="B9" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
@@ -1777,7 +1791,7 @@
         <v>1002</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -1789,10 +1803,10 @@
         <v>23</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:18">
@@ -1800,43 +1814,43 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D10" s="2">
         <v>4251434</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G10" s="2">
         <v>1005</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I10" s="2">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:18">
@@ -1844,10 +1858,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D11" s="2">
         <v>2222</v>
@@ -1868,19 +1882,19 @@
         <v>2</v>
       </c>
       <c r="J11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="N11" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:18">
@@ -1888,10 +1902,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D12" s="2">
         <v>2435135</v>
@@ -1912,19 +1926,19 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="N12" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1952,7 +1966,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:1">
